--- a/excel_files/overtime_2026-02-01_2026-02-28.xlsx
+++ b/excel_files/overtime_2026-02-01_2026-02-28.xlsx
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I49"/>
+  <dimension ref="A1:I126"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -1043,17 +1043,17 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>Западно-Лугинецкое</t>
+          <t>Шингинское</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>ГПН-В</t>
+          <t>ГПН-Автоматизация</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Бабаев Д.Н.</t>
+          <t>Жильцов Д.В.</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -1067,34 +1067,34 @@
         </is>
       </c>
       <c r="F14" s="3" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="G14" s="4" t="n">
         <v>15</v>
       </c>
       <c r="H14" s="5" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="I14" s="6" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>86.7%</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>Западно-Лугинецкое</t>
+          <t>Шингинское</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>ГПН-В</t>
+          <t>ГПН-Автоматизация</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Зозуля Ю.А.</t>
+          <t>Платонов С.В.</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -1108,34 +1108,34 @@
         </is>
       </c>
       <c r="F15" s="3" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="G15" s="4" t="n">
         <v>15</v>
       </c>
       <c r="H15" s="5" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="I15" s="6" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>86.7%</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>Западно-Лугинецкое</t>
+          <t>Шингинское</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>ГПН-В</t>
+          <t>ГПН-Автоматизация</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Кондратьев О.А</t>
+          <t>Солякин С.В.</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -1149,34 +1149,34 @@
         </is>
       </c>
       <c r="F16" s="3" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="G16" s="4" t="n">
         <v>15</v>
       </c>
       <c r="H16" s="5" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="I16" s="6" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>86.7%</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>Западно-Лугинецкое</t>
+          <t>Шингинское</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>ГПН-В</t>
+          <t>ГПН-Автоматизация</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Кондрашов С.С.</t>
+          <t>Шихалев В.И.</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -1190,24 +1190,24 @@
         </is>
       </c>
       <c r="F17" s="3" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="G17" s="4" t="n">
         <v>15</v>
       </c>
       <c r="H17" s="5" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="I17" s="6" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>86.7%</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>Западно-Лугинецкое</t>
+          <t>Шингинское</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -1217,7 +1217,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Корнеев П.О.</t>
+          <t>Андреев М.А.</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -1231,24 +1231,24 @@
         </is>
       </c>
       <c r="F18" s="3" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="G18" s="4" t="n">
         <v>15</v>
       </c>
       <c r="H18" s="5" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="I18" s="6" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>86.7%</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>Западно-Лугинецкое</t>
+          <t>Шингинское</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
@@ -1258,7 +1258,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Кутлияров А.П.</t>
+          <t>Воронецкий Д.В.</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -1272,24 +1272,24 @@
         </is>
       </c>
       <c r="F19" s="3" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="G19" s="4" t="n">
         <v>15</v>
       </c>
       <c r="H19" s="5" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="I19" s="6" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>86.7%</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>Западно-Лугинецкое</t>
+          <t>Шингинское</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -1299,7 +1299,7 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Мокеев Ю.В.</t>
+          <t>Малко Э.В.</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -1313,24 +1313,24 @@
         </is>
       </c>
       <c r="F20" s="3" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="G20" s="4" t="n">
         <v>15</v>
       </c>
       <c r="H20" s="5" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="I20" s="6" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>86.7%</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>Западно-Лугинецкое</t>
+          <t>Шингинское</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
@@ -1340,7 +1340,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Новейченко А.А.</t>
+          <t>Отставных А.Н.</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -1354,34 +1354,34 @@
         </is>
       </c>
       <c r="F21" s="3" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="G21" s="4" t="n">
         <v>15</v>
       </c>
       <c r="H21" s="5" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="I21" s="6" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>86.7%</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>Западно-Лугинецкое</t>
+          <t>Шингинское</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Партнеры Томск</t>
+          <t>ГПН-В</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Бубнова Н.А.</t>
+          <t>Петров Д.Е.</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -1395,24 +1395,24 @@
         </is>
       </c>
       <c r="F22" s="3" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="G22" s="4" t="n">
         <v>15</v>
       </c>
       <c r="H22" s="5" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="I22" s="6" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>86.7%</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>Западно-Лугинецкое</t>
+          <t>Шингинское</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
@@ -1422,7 +1422,7 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Трапезников А.С.</t>
+          <t>Стишенко О.И</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -1436,34 +1436,34 @@
         </is>
       </c>
       <c r="F23" s="3" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="G23" s="4" t="n">
         <v>15</v>
       </c>
       <c r="H23" s="5" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="I23" s="6" t="inlineStr">
         <is>
-          <t>46.7%</t>
+          <t>86.7%</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>Западно-Лугинецкое</t>
+          <t>Шингинское</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Сервис центр ЭПУ</t>
+          <t>ГПНВ</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Халлиулина Л.И.</t>
+          <t>Бабушкин Д.Б.</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -1477,34 +1477,34 @@
         </is>
       </c>
       <c r="F24" s="3" t="n">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="G24" s="4" t="n">
         <v>15</v>
       </c>
       <c r="H24" s="5" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="I24" s="6" t="inlineStr">
         <is>
-          <t>26.7%</t>
+          <t>86.7%</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>Западно-Лугинецкое</t>
+          <t>Шингинское</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>ГПН-Автоматизация</t>
+          <t>ГПНВ</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Попов Е.А.</t>
+          <t>Дорошкевич К.Ю.</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -1518,34 +1518,34 @@
         </is>
       </c>
       <c r="F25" s="3" t="n">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="G25" s="4" t="n">
         <v>15</v>
       </c>
       <c r="H25" s="5" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="I25" s="6" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>86.7%</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>Западно-Лугинецкое</t>
+          <t>Шингинское</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>ГПН-В</t>
+          <t>ООО "УТТ-Югра"</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Антонов А.В.</t>
+          <t>Дурбалов М.А.</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -1559,34 +1559,34 @@
         </is>
       </c>
       <c r="F26" s="3" t="n">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="G26" s="4" t="n">
         <v>15</v>
       </c>
       <c r="H26" s="5" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="I26" s="6" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>86.7%</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>Западно-Лугинецкое</t>
+          <t>Шингинское</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>ГПН-В</t>
+          <t>ООО ЧОП "Отечество-С"</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>Будылдин П.С.</t>
+          <t>Дяминов Д.И.</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -1600,34 +1600,34 @@
         </is>
       </c>
       <c r="F27" s="3" t="n">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="G27" s="4" t="n">
         <v>15</v>
       </c>
       <c r="H27" s="5" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="I27" s="6" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>86.7%</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>Западно-Лугинецкое</t>
+          <t>Шингинское</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>ГПН-В</t>
+          <t>ООО ЧОП "Отечество-С"</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Быковский В.</t>
+          <t>Дяминов Н.И.</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -1641,34 +1641,34 @@
         </is>
       </c>
       <c r="F28" s="3" t="n">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="G28" s="4" t="n">
         <v>15</v>
       </c>
       <c r="H28" s="5" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="I28" s="6" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>86.7%</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>Западно-Лугинецкое</t>
+          <t>Шингинское</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>ГПН-В</t>
+          <t>ООО ЧОП "Отечество-С"</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>Ганеев А.Р.</t>
+          <t>Корнеев В.Л.</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -1682,34 +1682,34 @@
         </is>
       </c>
       <c r="F29" s="3" t="n">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="G29" s="4" t="n">
         <v>15</v>
       </c>
       <c r="H29" s="5" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="I29" s="6" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>86.7%</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>Западно-Лугинецкое</t>
+          <t>Шингинское</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>ГПН-В</t>
+          <t>ООО ЧОП "Отечество-С"</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Гонина Е.Е.</t>
+          <t>Мездрин Е.В.</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -1723,34 +1723,34 @@
         </is>
       </c>
       <c r="F30" s="3" t="n">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="G30" s="4" t="n">
         <v>15</v>
       </c>
       <c r="H30" s="5" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="I30" s="6" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>86.7%</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>Западно-Лугинецкое</t>
+          <t>Шингинское</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>ГПН-В</t>
+          <t>Партнеры Томск</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Звягинцев А.В.</t>
+          <t>Береговая А.Ю.</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -1764,34 +1764,34 @@
         </is>
       </c>
       <c r="F31" s="3" t="n">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="G31" s="4" t="n">
         <v>15</v>
       </c>
       <c r="H31" s="5" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="I31" s="6" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>86.7%</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>Западно-Лугинецкое</t>
+          <t>Шингинское</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>ГПН-В</t>
+          <t>Партнеры Томск</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Иванов А.Г.</t>
+          <t>Гаус Н.В</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -1805,34 +1805,34 @@
         </is>
       </c>
       <c r="F32" s="3" t="n">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="G32" s="4" t="n">
         <v>15</v>
       </c>
       <c r="H32" s="5" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="I32" s="6" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>86.7%</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>Западно-Лугинецкое</t>
+          <t>Шингинское</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>ГПН-В</t>
+          <t>Партнеры Томск</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Колобов С.В.</t>
+          <t>Краморов Д.В.</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -1846,34 +1846,34 @@
         </is>
       </c>
       <c r="F33" s="3" t="n">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="G33" s="4" t="n">
         <v>15</v>
       </c>
       <c r="H33" s="5" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="I33" s="6" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>86.7%</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>Западно-Лугинецкое</t>
+          <t>Шингинское</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>ГПН-В</t>
+          <t>Партнеры Томск</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Конаков А.Н.</t>
+          <t>Мейлах Н.Г</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -1887,34 +1887,34 @@
         </is>
       </c>
       <c r="F34" s="3" t="n">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="G34" s="4" t="n">
         <v>15</v>
       </c>
       <c r="H34" s="5" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="I34" s="6" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>86.7%</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>Западно-Лугинецкое</t>
+          <t>Шингинское</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>ГПН-В</t>
+          <t>Партнеры Томск</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Константинов А.В.</t>
+          <t>Налепа Т.Б.</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -1928,34 +1928,34 @@
         </is>
       </c>
       <c r="F35" s="3" t="n">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="G35" s="4" t="n">
         <v>15</v>
       </c>
       <c r="H35" s="5" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="I35" s="6" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>86.7%</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>Западно-Лугинецкое</t>
+          <t>Шингинское</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>ГПН-В</t>
+          <t>СибМедЦентр</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Купчиков Д.А.</t>
+          <t>Евескин М.Ш.</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -1969,34 +1969,34 @@
         </is>
       </c>
       <c r="F36" s="3" t="n">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="G36" s="4" t="n">
         <v>15</v>
       </c>
       <c r="H36" s="5" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="I36" s="6" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>86.7%</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>Западно-Лугинецкое</t>
+          <t>Шингинское</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>ГПН-В</t>
+          <t>СибМедЦентр</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Левин М.М.</t>
+          <t>Смолякова Н.В.</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -2010,34 +2010,34 @@
         </is>
       </c>
       <c r="F37" s="3" t="n">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="G37" s="4" t="n">
         <v>15</v>
       </c>
       <c r="H37" s="5" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="I37" s="6" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>86.7%</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>Западно-Лугинецкое</t>
+          <t>Шингинское</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>ГПН-В</t>
+          <t>ТИТЦ</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Мартынов И.А.</t>
+          <t>Гребнев В.Г.</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -2051,34 +2051,34 @@
         </is>
       </c>
       <c r="F38" s="3" t="n">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="G38" s="4" t="n">
         <v>15</v>
       </c>
       <c r="H38" s="5" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="I38" s="6" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>86.7%</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>Западно-Лугинецкое</t>
+          <t>Шингинское</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>ГПН-В</t>
+          <t>ТИТЦ</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>Савинский С.В.</t>
+          <t>Колесников А.Г.</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
@@ -2092,34 +2092,34 @@
         </is>
       </c>
       <c r="F39" s="3" t="n">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="G39" s="4" t="n">
         <v>15</v>
       </c>
       <c r="H39" s="5" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="I39" s="6" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>86.7%</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>Западно-Лугинецкое</t>
+          <t>Шингинское</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>ГПН-В</t>
+          <t>ТИТЦ</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Школин К.М.</t>
+          <t>Мохнащеков А.В.</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -2133,34 +2133,34 @@
         </is>
       </c>
       <c r="F40" s="3" t="n">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="G40" s="4" t="n">
         <v>15</v>
       </c>
       <c r="H40" s="5" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="I40" s="6" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>86.7%</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>Западно-Лугинецкое</t>
+          <t>Шингинское</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>ГПН-Снабжение</t>
+          <t>ТИТЦ</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>Замараев Д.А.</t>
+          <t>Сапега А.С.</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
@@ -2174,34 +2174,34 @@
         </is>
       </c>
       <c r="F41" s="3" t="n">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="G41" s="4" t="n">
         <v>15</v>
       </c>
       <c r="H41" s="5" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="I41" s="6" t="inlineStr">
         <is>
-          <t>13.3%</t>
+          <t>86.7%</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>Западно-Лугинецкое</t>
+          <t>Шингинское</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>ГПН-Автоматизация</t>
+          <t>УТТ-Югра</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Колесов Ш.Р.</t>
+          <t>Долгов Д.А.</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
@@ -2215,34 +2215,34 @@
         </is>
       </c>
       <c r="F42" s="3" t="n">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="G42" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="H42" s="7" t="n">
-        <v>0</v>
+      <c r="H42" s="5" t="n">
+        <v>13</v>
       </c>
       <c r="I42" s="6" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>86.7%</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>Западно-Лугинецкое</t>
+          <t>Шингинское</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>ГПН-Автоматизация</t>
+          <t>УТТ-Югра</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>Урюпов  А.Е.</t>
+          <t>Косарев Д.А.</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
@@ -2256,34 +2256,34 @@
         </is>
       </c>
       <c r="F43" s="3" t="n">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="G43" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="H43" s="7" t="n">
-        <v>0</v>
+      <c r="H43" s="5" t="n">
+        <v>13</v>
       </c>
       <c r="I43" s="6" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>86.7%</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>Западно-Лугинецкое</t>
+          <t>Шингинское</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>ГПН-В</t>
+          <t>ГПН-Автоматизация</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Зандер Д.Э.</t>
+          <t>Попов Е.А.</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
@@ -2297,34 +2297,34 @@
         </is>
       </c>
       <c r="F44" s="3" t="n">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="G44" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="H44" s="7" t="n">
-        <v>0</v>
+      <c r="H44" s="5" t="n">
+        <v>12</v>
       </c>
       <c r="I44" s="6" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>80.0%</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>Западно-Лугинецкое</t>
+          <t>Шингинское</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>ГПН-В</t>
+          <t>ГПН-Автоматизация</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>Ряполов Б.Н.</t>
+          <t>Спиридонов Я.Э.</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
@@ -2338,34 +2338,34 @@
         </is>
       </c>
       <c r="F45" s="3" t="n">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="G45" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="H45" s="7" t="n">
-        <v>0</v>
+      <c r="H45" s="5" t="n">
+        <v>11</v>
       </c>
       <c r="I45" s="6" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>73.3%</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>Западно-Лугинецкое</t>
+          <t>Шингинское</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>ГПН-В</t>
+          <t>МСБ</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>Смирнов Д.И.</t>
+          <t>Марущак А.И.</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
@@ -2379,17 +2379,17 @@
         </is>
       </c>
       <c r="F46" s="3" t="n">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="G46" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="H46" s="7" t="n">
-        <v>0</v>
+      <c r="H46" s="5" t="n">
+        <v>11</v>
       </c>
       <c r="I46" s="6" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>73.3%</t>
         </is>
       </c>
     </row>
@@ -2401,12 +2401,12 @@
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>ООО   "ТрансСервис"</t>
+          <t>ГПН-В</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>Сидельцев Д.М.</t>
+          <t>Зозуля Ю.А.</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
@@ -2420,17 +2420,17 @@
         </is>
       </c>
       <c r="F47" s="3" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="G47" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="H47" s="7" t="n">
-        <v>0</v>
+      <c r="H47" s="5" t="n">
+        <v>10</v>
       </c>
       <c r="I47" s="6" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
@@ -2442,57 +2442,3214 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
+          <t>ГПН-В</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>Кондратьев О.А</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>01.02.2026</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>28.02.2026</t>
+        </is>
+      </c>
+      <c r="F48" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="G48" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="H48" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="I48" s="6" t="inlineStr">
+        <is>
+          <t>66.7%</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>Западно-Лугинецкое</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>ГПН-В</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>Кондрашов С.С.</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>01.02.2026</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>28.02.2026</t>
+        </is>
+      </c>
+      <c r="F49" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="G49" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="H49" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="I49" s="6" t="inlineStr">
+        <is>
+          <t>66.7%</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>Западно-Лугинецкое</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>ГПН-В</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>Корнеев П.О.</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>01.02.2026</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>28.02.2026</t>
+        </is>
+      </c>
+      <c r="F50" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="G50" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="H50" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="I50" s="6" t="inlineStr">
+        <is>
+          <t>66.7%</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>Западно-Лугинецкое</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>ГПН-В</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>Кутлияров А.П.</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>01.02.2026</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>28.02.2026</t>
+        </is>
+      </c>
+      <c r="F51" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="G51" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="H51" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="I51" s="6" t="inlineStr">
+        <is>
+          <t>66.7%</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>Западно-Лугинецкое</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>ГПН-В</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>Мокеев Ю.В.</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>01.02.2026</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>28.02.2026</t>
+        </is>
+      </c>
+      <c r="F52" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="G52" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="H52" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="I52" s="6" t="inlineStr">
+        <is>
+          <t>66.7%</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>Западно-Лугинецкое</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>ГПН-В</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>Новейченко А.А.</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>01.02.2026</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>28.02.2026</t>
+        </is>
+      </c>
+      <c r="F53" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="G53" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="H53" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="I53" s="6" t="inlineStr">
+        <is>
+          <t>66.7%</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>Западно-Лугинецкое</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
           <t>Партнеры Томск</t>
         </is>
       </c>
-      <c r="C48" s="2" t="inlineStr">
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>Бубнова Н.А.</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>01.02.2026</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>28.02.2026</t>
+        </is>
+      </c>
+      <c r="F54" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="G54" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="H54" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="I54" s="6" t="inlineStr">
+        <is>
+          <t>66.7%</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>Шингинское</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>ГПН-Автоматизация</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>Колесов Ш.Р.</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>01.02.2026</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>28.02.2026</t>
+        </is>
+      </c>
+      <c r="F55" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="G55" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="H55" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="I55" s="6" t="inlineStr">
+        <is>
+          <t>66.7%</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>Шингинское</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>ГПН-В</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>Гончаров А.С.</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>01.02.2026</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>28.02.2026</t>
+        </is>
+      </c>
+      <c r="F56" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="G56" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="H56" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="I56" s="6" t="inlineStr">
+        <is>
+          <t>66.7%</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>Шингинское</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>ГПН-В</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>Купчиков Д.А.</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>01.02.2026</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>28.02.2026</t>
+        </is>
+      </c>
+      <c r="F57" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="G57" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="H57" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="I57" s="6" t="inlineStr">
+        <is>
+          <t>66.7%</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>Шингинское</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>ГПН-В</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>Тардаскин В.П.</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>01.02.2026</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>28.02.2026</t>
+        </is>
+      </c>
+      <c r="F58" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="G58" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="H58" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="I58" s="6" t="inlineStr">
+        <is>
+          <t>66.7%</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>Шингинское</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>ГПН-В</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>Яровой Д.В.</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>01.02.2026</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>28.02.2026</t>
+        </is>
+      </c>
+      <c r="F59" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="G59" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="H59" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="I59" s="6" t="inlineStr">
+        <is>
+          <t>66.7%</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>Шингинское</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>ГПНВ</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>Купалов О.А.</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>01.02.2026</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>28.02.2026</t>
+        </is>
+      </c>
+      <c r="F60" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="G60" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="H60" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="I60" s="6" t="inlineStr">
+        <is>
+          <t>66.7%</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>Шингинское</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>ГПНВ</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>Нестеров Н.Ю.</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>01.02.2026</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>28.02.2026</t>
+        </is>
+      </c>
+      <c r="F61" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="G61" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="H61" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="I61" s="6" t="inlineStr">
+        <is>
+          <t>66.7%</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>Шингинское</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>ГПНВ</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>Попов А.А.</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>01.02.2026</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>28.02.2026</t>
+        </is>
+      </c>
+      <c r="F62" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="G62" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="H62" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="I62" s="6" t="inlineStr">
+        <is>
+          <t>66.7%</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>Шингинское</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>ГПНВ</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>Ряполов Б.Н</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>01.02.2026</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>28.02.2026</t>
+        </is>
+      </c>
+      <c r="F63" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="G63" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="H63" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="I63" s="6" t="inlineStr">
+        <is>
+          <t>66.7%</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>Шингинское</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>ГПНВ</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>Сахно М.Ю.</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>01.02.2026</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>28.02.2026</t>
+        </is>
+      </c>
+      <c r="F64" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="G64" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="H64" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="I64" s="6" t="inlineStr">
+        <is>
+          <t>66.7%</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>Шингинское</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>ГПНВ</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>Смирнов Д.И.</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>01.02.2026</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>28.02.2026</t>
+        </is>
+      </c>
+      <c r="F65" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="G65" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="H65" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="I65" s="6" t="inlineStr">
+        <is>
+          <t>66.7%</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>Шингинское</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>ГПНВ</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>Худорожко А.С.</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>01.02.2026</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>28.02.2026</t>
+        </is>
+      </c>
+      <c r="F66" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="G66" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="H66" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="I66" s="6" t="inlineStr">
+        <is>
+          <t>66.7%</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>Шингинское</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>ГПНВ</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>Шеверов В.В.</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>01.02.2026</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>28.02.2026</t>
+        </is>
+      </c>
+      <c r="F67" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="G67" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="H67" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="I67" s="6" t="inlineStr">
+        <is>
+          <t>66.7%</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>Шингинское</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>ГПНВ</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>Шигаев Д.В.</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>01.02.2026</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>28.02.2026</t>
+        </is>
+      </c>
+      <c r="F68" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="G68" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="H68" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="I68" s="6" t="inlineStr">
+        <is>
+          <t>66.7%</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>Шингинское</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>ГПНВ</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>Казакова Э.Ф.</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>01.02.2026</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>28.02.2026</t>
+        </is>
+      </c>
+      <c r="F69" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="G69" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="H69" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="I69" s="6" t="inlineStr">
+        <is>
+          <t>60.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>Шингинское</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>ГПН-В</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>Чигвинцев М.А.</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>01.02.2026</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>28.02.2026</t>
+        </is>
+      </c>
+      <c r="F70" s="3" t="n">
+        <v>23</v>
+      </c>
+      <c r="G70" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="H70" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="I70" s="6" t="inlineStr">
+        <is>
+          <t>53.3%</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>Западно-Лугинецкое</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>ГПН-В</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>Трапезников А.С.</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>01.02.2026</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>28.02.2026</t>
+        </is>
+      </c>
+      <c r="F71" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="G71" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="H71" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="I71" s="6" t="inlineStr">
+        <is>
+          <t>46.7%</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>Шингинское</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>ГПН-Автоматизация</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>Асылгареев М.Р.</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>01.02.2026</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>28.02.2026</t>
+        </is>
+      </c>
+      <c r="F72" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="G72" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="H72" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="I72" s="6" t="inlineStr">
+        <is>
+          <t>46.7%</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>Шингинское</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>ГПНВ</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>Терентьев Д.А.</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>01.02.2026</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>28.02.2026</t>
+        </is>
+      </c>
+      <c r="F73" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="G73" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="H73" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="I73" s="6" t="inlineStr">
+        <is>
+          <t>46.7%</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>Шингинское</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>ГПНВ</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>Гламозда И.В.</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>01.02.2026</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>28.02.2026</t>
+        </is>
+      </c>
+      <c r="F74" s="3" t="n">
+        <v>21</v>
+      </c>
+      <c r="G74" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="H74" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="I74" s="6" t="inlineStr">
+        <is>
+          <t>40.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>Шингинское</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>ГПНВ</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>Зандер Д.Э.</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>01.02.2026</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>28.02.2026</t>
+        </is>
+      </c>
+      <c r="F75" s="3" t="n">
+        <v>21</v>
+      </c>
+      <c r="G75" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="H75" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="I75" s="6" t="inlineStr">
+        <is>
+          <t>40.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>Шингинское</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>ООО " Русэнерго"</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>Давыдченко Д.Ю.</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>01.02.2026</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>28.02.2026</t>
+        </is>
+      </c>
+      <c r="F76" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="G76" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="H76" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="I76" s="6" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>Шингинское</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>ООО " Русэнерго"</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>Шершнев Е.М.</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>01.02.2026</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>28.02.2026</t>
+        </is>
+      </c>
+      <c r="F77" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="G77" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="H77" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="I77" s="6" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>Западно-Лугинецкое</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>Сервис центр ЭПУ</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>Халлиулина Л.И.</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>01.02.2026</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>28.02.2026</t>
+        </is>
+      </c>
+      <c r="F78" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="G78" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="H78" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="I78" s="6" t="inlineStr">
+        <is>
+          <t>26.7%</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>Шингинское</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>ГПН-Автоматизация</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>Манашев Р.Ю.</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>01.02.2026</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>28.02.2026</t>
+        </is>
+      </c>
+      <c r="F79" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="G79" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="H79" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="I79" s="6" t="inlineStr">
+        <is>
+          <t>26.7%</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>Шингинское</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>ГПН-Автоматизация</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>Талицких М.В.</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>01.02.2026</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>28.02.2026</t>
+        </is>
+      </c>
+      <c r="F80" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="G80" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="H80" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="I80" s="6" t="inlineStr">
+        <is>
+          <t>26.7%</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>Шингинское</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>ГПН-Автоматизация</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>Юн В.В.</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>01.02.2026</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>28.02.2026</t>
+        </is>
+      </c>
+      <c r="F81" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="G81" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="H81" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="I81" s="6" t="inlineStr">
+        <is>
+          <t>26.7%</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>Шингинское</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>ГПН-ИТО</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>Филимонов К.В.</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>01.02.2026</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>28.02.2026</t>
+        </is>
+      </c>
+      <c r="F82" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="G82" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="H82" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="I82" s="6" t="inlineStr">
+        <is>
+          <t>26.7%</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>Западно-Лугинецкое</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>ГПН-Автоматизация</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>Попов Е.А.</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>01.02.2026</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>28.02.2026</t>
+        </is>
+      </c>
+      <c r="F83" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="G83" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="H83" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="I83" s="6" t="inlineStr">
+        <is>
+          <t>20.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>Западно-Лугинецкое</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>ГПН-В</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>Антонов А.В.</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>01.02.2026</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>28.02.2026</t>
+        </is>
+      </c>
+      <c r="F84" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="G84" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="H84" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="I84" s="6" t="inlineStr">
+        <is>
+          <t>20.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>Западно-Лугинецкое</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>ГПН-В</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>Будылдин П.С.</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>01.02.2026</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>28.02.2026</t>
+        </is>
+      </c>
+      <c r="F85" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="G85" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="H85" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="I85" s="6" t="inlineStr">
+        <is>
+          <t>20.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>Западно-Лугинецкое</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>ГПН-В</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>Быковский В.</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>01.02.2026</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>28.02.2026</t>
+        </is>
+      </c>
+      <c r="F86" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="G86" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="H86" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="I86" s="6" t="inlineStr">
+        <is>
+          <t>20.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>Западно-Лугинецкое</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>ГПН-В</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>Ганеев А.Р.</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>01.02.2026</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>28.02.2026</t>
+        </is>
+      </c>
+      <c r="F87" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="G87" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="H87" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="I87" s="6" t="inlineStr">
+        <is>
+          <t>20.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>Западно-Лугинецкое</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>ГПН-В</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>Гонина Е.Е.</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>01.02.2026</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>28.02.2026</t>
+        </is>
+      </c>
+      <c r="F88" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="G88" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="H88" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="I88" s="6" t="inlineStr">
+        <is>
+          <t>20.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>Западно-Лугинецкое</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>ГПН-В</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>Звягинцев А.В.</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>01.02.2026</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>28.02.2026</t>
+        </is>
+      </c>
+      <c r="F89" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="G89" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="H89" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="I89" s="6" t="inlineStr">
+        <is>
+          <t>20.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>Западно-Лугинецкое</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>ГПН-В</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>Иванов А.Г.</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>01.02.2026</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>28.02.2026</t>
+        </is>
+      </c>
+      <c r="F90" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="G90" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="H90" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="I90" s="6" t="inlineStr">
+        <is>
+          <t>20.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>Западно-Лугинецкое</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>ГПН-В</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>Колобов С.В.</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>01.02.2026</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>28.02.2026</t>
+        </is>
+      </c>
+      <c r="F91" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="G91" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="H91" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="I91" s="6" t="inlineStr">
+        <is>
+          <t>20.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>Западно-Лугинецкое</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>ГПН-В</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>Конаков А.Н.</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>01.02.2026</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>28.02.2026</t>
+        </is>
+      </c>
+      <c r="F92" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="G92" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="H92" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="I92" s="6" t="inlineStr">
+        <is>
+          <t>20.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>Западно-Лугинецкое</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>ГПН-В</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>Константинов А.В.</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>01.02.2026</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>28.02.2026</t>
+        </is>
+      </c>
+      <c r="F93" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="G93" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="H93" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="I93" s="6" t="inlineStr">
+        <is>
+          <t>20.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>Западно-Лугинецкое</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>ГПН-В</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>Купчиков Д.А.</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>01.02.2026</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>28.02.2026</t>
+        </is>
+      </c>
+      <c r="F94" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="G94" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="H94" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="I94" s="6" t="inlineStr">
+        <is>
+          <t>20.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>Западно-Лугинецкое</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>ГПН-В</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>Левин М.М.</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>01.02.2026</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>28.02.2026</t>
+        </is>
+      </c>
+      <c r="F95" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="G95" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="H95" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="I95" s="6" t="inlineStr">
+        <is>
+          <t>20.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>Западно-Лугинецкое</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>ГПН-В</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>Мартынов И.А.</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>01.02.2026</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>28.02.2026</t>
+        </is>
+      </c>
+      <c r="F96" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="G96" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="H96" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="I96" s="6" t="inlineStr">
+        <is>
+          <t>20.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>Западно-Лугинецкое</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>ГПН-В</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>Савинский С.В.</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>01.02.2026</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>28.02.2026</t>
+        </is>
+      </c>
+      <c r="F97" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="G97" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="H97" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="I97" s="6" t="inlineStr">
+        <is>
+          <t>20.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>Западно-Лугинецкое</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>ГПН-В</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>Школин К.М.</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>01.02.2026</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>28.02.2026</t>
+        </is>
+      </c>
+      <c r="F98" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="G98" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="H98" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="I98" s="6" t="inlineStr">
+        <is>
+          <t>20.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>Шингинское</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>ГПН-Автоматизация</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>Давыдов Д.А.</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>01.02.2026</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>28.02.2026</t>
+        </is>
+      </c>
+      <c r="F99" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="G99" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="H99" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="I99" s="6" t="inlineStr">
+        <is>
+          <t>20.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>Шингинское</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>ГПН-В</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>Кузнецов В.М.</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>01.02.2026</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>28.02.2026</t>
+        </is>
+      </c>
+      <c r="F100" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="G100" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="H100" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="I100" s="6" t="inlineStr">
+        <is>
+          <t>20.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>Шингинское</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>ГПН-В</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>Попов М.А.</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>01.02.2026</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t>28.02.2026</t>
+        </is>
+      </c>
+      <c r="F101" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="G101" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="H101" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="I101" s="6" t="inlineStr">
+        <is>
+          <t>20.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>Шингинское</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>ГПН-В</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>Талынов Н.С.</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>01.02.2026</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>28.02.2026</t>
+        </is>
+      </c>
+      <c r="F102" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="G102" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="H102" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="I102" s="6" t="inlineStr">
+        <is>
+          <t>20.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>Шингинское</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>ГПНВ</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>Бурдуков А.Н.</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>01.02.2026</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr">
+        <is>
+          <t>28.02.2026</t>
+        </is>
+      </c>
+      <c r="F103" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="G103" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="H103" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="I103" s="6" t="inlineStr">
+        <is>
+          <t>20.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>Шингинское</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>ГПНВ</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>Кунин М.И.</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>01.02.2026</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="inlineStr">
+        <is>
+          <t>28.02.2026</t>
+        </is>
+      </c>
+      <c r="F104" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="G104" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="H104" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="I104" s="6" t="inlineStr">
+        <is>
+          <t>20.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
+        <is>
+          <t>Шингинское</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>ГПНВ</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>Купалов Д.А.</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
+        <is>
+          <t>01.02.2026</t>
+        </is>
+      </c>
+      <c r="E105" s="2" t="inlineStr">
+        <is>
+          <t>28.02.2026</t>
+        </is>
+      </c>
+      <c r="F105" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="G105" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="H105" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="I105" s="6" t="inlineStr">
+        <is>
+          <t>20.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>Шингинское</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>ГПНВ</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>Макаев И.Р.</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
+        <is>
+          <t>01.02.2026</t>
+        </is>
+      </c>
+      <c r="E106" s="2" t="inlineStr">
+        <is>
+          <t>28.02.2026</t>
+        </is>
+      </c>
+      <c r="F106" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="G106" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="H106" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="I106" s="6" t="inlineStr">
+        <is>
+          <t>20.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
+        <is>
+          <t>Шингинское</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>ГПНВ</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>Мамец А.С.</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
+        <is>
+          <t>01.02.2026</t>
+        </is>
+      </c>
+      <c r="E107" s="2" t="inlineStr">
+        <is>
+          <t>28.02.2026</t>
+        </is>
+      </c>
+      <c r="F107" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="G107" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="H107" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="I107" s="6" t="inlineStr">
+        <is>
+          <t>20.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>Шингинское</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>ГПНВ</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>Москвин В.В.</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
+        <is>
+          <t>01.02.2026</t>
+        </is>
+      </c>
+      <c r="E108" s="2" t="inlineStr">
+        <is>
+          <t>28.02.2026</t>
+        </is>
+      </c>
+      <c r="F108" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="G108" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="H108" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="I108" s="6" t="inlineStr">
+        <is>
+          <t>20.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
+        <is>
+          <t>Шингинское</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>ГПНВ</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>Русаков К.Е.</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
+        <is>
+          <t>01.02.2026</t>
+        </is>
+      </c>
+      <c r="E109" s="2" t="inlineStr">
+        <is>
+          <t>28.02.2026</t>
+        </is>
+      </c>
+      <c r="F109" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="G109" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="H109" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="I109" s="6" t="inlineStr">
+        <is>
+          <t>20.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>Шингинское</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>ГПНВ</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>Сайнаков Д.П.</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
+        <is>
+          <t>01.02.2026</t>
+        </is>
+      </c>
+      <c r="E110" s="2" t="inlineStr">
+        <is>
+          <t>28.02.2026</t>
+        </is>
+      </c>
+      <c r="F110" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="G110" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="H110" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="I110" s="6" t="inlineStr">
+        <is>
+          <t>20.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
+        <is>
+          <t>Шингинское</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>ГПНВ</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>Тимофеев Е.Г.</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
+        <is>
+          <t>01.02.2026</t>
+        </is>
+      </c>
+      <c r="E111" s="2" t="inlineStr">
+        <is>
+          <t>28.02.2026</t>
+        </is>
+      </c>
+      <c r="F111" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="G111" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="H111" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="I111" s="6" t="inlineStr">
+        <is>
+          <t>20.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
+        <is>
+          <t>Шингинское</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>ГПНВ</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>Тимощенко Д.А.</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
+        <is>
+          <t>01.02.2026</t>
+        </is>
+      </c>
+      <c r="E112" s="2" t="inlineStr">
+        <is>
+          <t>28.02.2026</t>
+        </is>
+      </c>
+      <c r="F112" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="G112" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="H112" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="I112" s="6" t="inlineStr">
+        <is>
+          <t>20.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
+        <is>
+          <t>Шингинское</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>ГПНВ</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>Федоров А.С.</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="inlineStr">
+        <is>
+          <t>01.02.2026</t>
+        </is>
+      </c>
+      <c r="E113" s="2" t="inlineStr">
+        <is>
+          <t>28.02.2026</t>
+        </is>
+      </c>
+      <c r="F113" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="G113" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="H113" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="I113" s="6" t="inlineStr">
+        <is>
+          <t>20.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
+        <is>
+          <t>Шингинское</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>ГПНВ</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>Чудиновский А.О.</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
+        <is>
+          <t>01.02.2026</t>
+        </is>
+      </c>
+      <c r="E114" s="2" t="inlineStr">
+        <is>
+          <t>28.02.2026</t>
+        </is>
+      </c>
+      <c r="F114" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="G114" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="H114" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="I114" s="6" t="inlineStr">
+        <is>
+          <t>20.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
+        <is>
+          <t>Западно-Лугинецкое</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>ГПН-Снабжение</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>Замараев Д.А.</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="inlineStr">
+        <is>
+          <t>01.02.2026</t>
+        </is>
+      </c>
+      <c r="E115" s="2" t="inlineStr">
+        <is>
+          <t>28.02.2026</t>
+        </is>
+      </c>
+      <c r="F115" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="G115" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="H115" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="I115" s="6" t="inlineStr">
+        <is>
+          <t>13.3%</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>Шингинское</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>ИнТех</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>Дмитриев И.Ю.</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr">
+        <is>
+          <t>01.02.2026</t>
+        </is>
+      </c>
+      <c r="E116" s="2" t="inlineStr">
+        <is>
+          <t>28.02.2026</t>
+        </is>
+      </c>
+      <c r="F116" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="G116" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="H116" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="I116" s="6" t="inlineStr">
+        <is>
+          <t>13.3%</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
+        <is>
+          <t>Шингинское</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>ИнТех</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>Тихонов А.Ю.</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="inlineStr">
+        <is>
+          <t>01.02.2026</t>
+        </is>
+      </c>
+      <c r="E117" s="2" t="inlineStr">
+        <is>
+          <t>28.02.2026</t>
+        </is>
+      </c>
+      <c r="F117" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="G117" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="H117" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="I117" s="6" t="inlineStr">
+        <is>
+          <t>13.3%</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
+        <is>
+          <t>Шингинское</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>ООО ЧОП "Отечество-С"</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>Носивец И.В.</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="inlineStr">
+        <is>
+          <t>01.02.2026</t>
+        </is>
+      </c>
+      <c r="E118" s="2" t="inlineStr">
+        <is>
+          <t>28.02.2026</t>
+        </is>
+      </c>
+      <c r="F118" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="G118" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="H118" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="I118" s="6" t="inlineStr">
+        <is>
+          <t>13.3%</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
+        <is>
+          <t>Западно-Лугинецкое</t>
+        </is>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t>ГПН-Автоматизация</t>
+        </is>
+      </c>
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>Колесов Ш.Р.</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="inlineStr">
+        <is>
+          <t>01.02.2026</t>
+        </is>
+      </c>
+      <c r="E119" s="2" t="inlineStr">
+        <is>
+          <t>28.02.2026</t>
+        </is>
+      </c>
+      <c r="F119" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="G119" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="H119" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I119" s="6" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
+        <is>
+          <t>Западно-Лугинецкое</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>ГПН-Автоматизация</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>Урюпов  А.Е.</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="inlineStr">
+        <is>
+          <t>01.02.2026</t>
+        </is>
+      </c>
+      <c r="E120" s="2" t="inlineStr">
+        <is>
+          <t>28.02.2026</t>
+        </is>
+      </c>
+      <c r="F120" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="G120" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="H120" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I120" s="6" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
+        <is>
+          <t>Западно-Лугинецкое</t>
+        </is>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>ГПН-В</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>Зандер Д.Э.</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="inlineStr">
+        <is>
+          <t>01.02.2026</t>
+        </is>
+      </c>
+      <c r="E121" s="2" t="inlineStr">
+        <is>
+          <t>28.02.2026</t>
+        </is>
+      </c>
+      <c r="F121" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="G121" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="H121" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I121" s="6" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
+        <is>
+          <t>Западно-Лугинецкое</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>ГПН-В</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>Ряполов Б.Н.</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="inlineStr">
+        <is>
+          <t>01.02.2026</t>
+        </is>
+      </c>
+      <c r="E122" s="2" t="inlineStr">
+        <is>
+          <t>28.02.2026</t>
+        </is>
+      </c>
+      <c r="F122" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="G122" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="H122" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I122" s="6" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
+        <is>
+          <t>Западно-Лугинецкое</t>
+        </is>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>ГПН-В</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>Смирнов Д.И.</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="inlineStr">
+        <is>
+          <t>01.02.2026</t>
+        </is>
+      </c>
+      <c r="E123" s="2" t="inlineStr">
+        <is>
+          <t>28.02.2026</t>
+        </is>
+      </c>
+      <c r="F123" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="G123" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="H123" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I123" s="6" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
+        <is>
+          <t>Западно-Лугинецкое</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>ООО   "ТрансСервис"</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>Сидельцев Д.М.</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="inlineStr">
+        <is>
+          <t>01.02.2026</t>
+        </is>
+      </c>
+      <c r="E124" s="2" t="inlineStr">
+        <is>
+          <t>28.02.2026</t>
+        </is>
+      </c>
+      <c r="F124" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="G124" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="H124" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I124" s="6" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
+        <is>
+          <t>Западно-Лугинецкое</t>
+        </is>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>Партнеры Томск</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="inlineStr">
         <is>
           <t>Налепа Т.Б.</t>
         </is>
       </c>
-      <c r="D48" s="2" t="inlineStr">
-        <is>
-          <t>01.02.2026</t>
-        </is>
-      </c>
-      <c r="E48" s="2" t="inlineStr">
-        <is>
-          <t>28.02.2026</t>
-        </is>
-      </c>
-      <c r="F48" s="3" t="n">
-        <v>15</v>
-      </c>
-      <c r="G48" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="H48" s="7" t="n">
+      <c r="D125" s="2" t="inlineStr">
+        <is>
+          <t>01.02.2026</t>
+        </is>
+      </c>
+      <c r="E125" s="2" t="inlineStr">
+        <is>
+          <t>28.02.2026</t>
+        </is>
+      </c>
+      <c r="F125" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="G125" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="H125" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="I48" s="6" t="inlineStr">
+      <c r="I125" s="6" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="8" t="inlineStr">
+    <row r="126">
+      <c r="A126" s="8" t="inlineStr">
         <is>
           <t>ИТОГО</t>
         </is>
       </c>
-      <c r="B49" s="8" t="n"/>
-      <c r="C49" s="8" t="n"/>
-      <c r="D49" s="8" t="n"/>
-      <c r="E49" s="8" t="n"/>
-      <c r="F49" s="8" t="n">
-        <v>1012</v>
-      </c>
-      <c r="G49" s="8" t="n"/>
-      <c r="H49" s="8" t="n">
-        <v>307</v>
-      </c>
-      <c r="I49" s="8" t="n"/>
+      <c r="B126" s="8" t="n"/>
+      <c r="C126" s="8" t="n"/>
+      <c r="D126" s="8" t="n"/>
+      <c r="E126" s="8" t="n"/>
+      <c r="F126" s="8" t="n">
+        <v>2844</v>
+      </c>
+      <c r="G126" s="8" t="n"/>
+      <c r="H126" s="8" t="n">
+        <v>984</v>
+      </c>
+      <c r="I126" s="8" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
